--- a/stage_2.xlsx
+++ b/stage_2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,1966 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>931311984</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>@m_rq9</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>منتظر امجد ابراهيم</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ياسين خريبط</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:56:32.197</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7238142091</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>@bgx_q</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>حسين محمد حسن</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>الحيانيه</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:58:48.936</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1497554239</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>@Stella_4h</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>سارة محمد صادق</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:59:55.275</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5910511136</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>@zan_9f</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>زينب مجيد محسن</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>كرمة علي</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-14 17:59:59.953</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1490369447</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>@Vv8nv</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>لاسم:محمد باقر حسين احمد يعقوب</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>العنوان: المطيحه</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:01.184</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1343735603</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>@ve5cc</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>عقيل مسلم عبيد</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:10.875</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1438751044</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>@alsyab1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>احمد حسين خليل</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>المطيحة</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:17.530</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5169066471</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>@Luc_i2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>حسن عبد الهادي ربيع</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>المعقل</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>الشركة العامة لموانئ العراق</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:20.325</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1726535932</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>@raw_9q</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>رونق صالح حمدي</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>المعقل</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:21.799</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1697561654</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>@lb_ci5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>فاطمة محمد خالد</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>المشراق القديم</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:35.939</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8386221117</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>@hadier177</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>حيدر عبد الرحمن جواد</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>قضاء المدينة</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:36.756</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5532563451</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>@dem_iq</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ديمه سمير عبدالله</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>الجمعيات الرابعة</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>الشركة العامة لموانئ العراق</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:37.926</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1447876418</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>@ioilo_ili</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ايمان عيسى راضي</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>الزبير  حي الشهداء</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>شركة الحفر العراقية</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:43.986</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>973839925</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>@Hidory_noory</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>حيدر نوري حسيب</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>خور الزبير</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>الشركة العامة للحديد والصلب</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:48.710</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1395998266</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>@B18ano</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>بنين جواد كاظم</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>الاصمعي القديم</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:00:57.787</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>5587310421</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>@c_h9o</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>الاسم:حسن رافد سلام</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>الموقع :ابي الخصيب</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (البصرة)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:01:17.370</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1758155606</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>@s_aj_d4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>سجاد صفاء جبار</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>خمسة ميل</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:01:52.372</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2111133490</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>@JINIRAL_5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>علي سجاد حسين</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>كوت الحجاج</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:02:22.103</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2079194390</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>@CHRO1LUC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>حسنين محسن عبيد</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>القرنة - الشرش</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:02:25.568</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1371183148</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>@Al_Moussawiii</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>عبدالله اسعد جبار</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>القبلة /حي الشهداء</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:02:51.449</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>966780550</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>@ta_2h4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>طه مال الله عبد الرضا</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>خور الزبير</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>الشركة العامة للحديد والصلب</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:03:01.198</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8163635407</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>زكي مناف صالح</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>حي بغداد</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:03:21.345</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7600878112</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>@sxkxh</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>شذى عمار عبد الله</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ابي الخصيب الاسمدة</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>مركز التدريب المهني</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:03:21.942</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>914756387</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>@p_bi1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>مجتبى محمد سلمان</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>القرنة الشرش</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:06:46.551</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1004621723</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>@Sadi9q9</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>صادق خالد ناصر</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>حي الاصدقاء</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:07:42.717</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>604685914</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>@Ykkojg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>زينب هاني عبد الزهره</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>الزبير</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>شركة الحفر العراقية</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:08:40.873</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>405791459</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>@zf_lv</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>سجى احمد هاشم</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>مجمع الامل السكني</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:11:03.077</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1430214454</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>@Asmaa_64</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>اسماء وليد فالح</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>القرنة</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:12:27.483</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1125968403</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>@K93N92</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>كرار عربي صالح</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>التنومة /الصالحية</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:14:16.806</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1551714319</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>@s0_0_j</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>سجاد جمعة محسن</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>قضاء الامام الصادق (ع)/ ابو غريب</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:18:02.786</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7025359562</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>اسماء وليد فالح</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>القرنة</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:18:34.788</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>822308309</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>@adh_p</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>علي جبار صالح</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>شط العرب الجزيرة_ الفيروزية</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:23:16.315</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1236724280</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>@rno_onr</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>نور رعد ظاهر</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>القبلة حي القائم</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:25:00.795</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1524690305</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>@mjrmiq</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>عبد الصمد نزار حمد</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>طلحة الجاسم (قضاء الامام الصادق)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>توزيع كهرباء الجنوب (شمال البصرة)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:25:10.639</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1249011951</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>@X_e7K</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>محمد ثائر عبد الباري</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>العشار شارع الاستقلال</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>معهد التدريب النفطي</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:34:09.315</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>7564375153</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>@As1Asm</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>علي احمد تعبان</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>كوت الحجاج الثانيه</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>المديرية العامة لنقل الطاقة</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:42:23.127</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1611740483</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>@aa70y</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>احمد رياض علي</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ابي الخصيب _ باب طويل</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-05-14 18:50:19.960</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>824383352</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>@alihayder_0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>علي علي حيدر</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>گرمة علي</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-05-14 19:00:04.127</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1400015616</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>@ad_ali8</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>احمد عبد علي كاظم</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>الدير ناحية المصطفى</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-05-14 19:28:48.568</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1021572453</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>@shmikh2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>مصطفى حمود كاظم</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>الزبير الصحفيين الثانية</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-05-14 19:41:51.907</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>6946319674</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>كرار حيدر شيال</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ابوخصيب فجة العرب</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>المديرية العامة لإنتاج الطاقة</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-05-14 20:13:45.149</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>8041135766</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>@zahj00378</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>زهراء جعفر خليل</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>شط العرب /التنومة</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>شركة الحفر العراقية</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-05-14 21:15:32.639</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>7109414182</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>@Kko55l</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>الاسم محمد المصطفى عمار قاسم</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>البصرة الموفقيه الاملاك</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>الشركة العامة للحديد والصلب</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-05-14 21:44:03.304</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1497074020</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>كرار صادق شهاب</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>أبي الخصيب السبيليات</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>شركة تعبئة وخدمات الغاز</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-05-15 07:37:51.239</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>7886566070</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>@idekuu12</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>امجد جلال امجد</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>قبلة-حي المهندسين</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-05-16 01:02:34.763</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>8712630269</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>@roro44_r</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>رقية جمعة عودة</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>الدير</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>شركة ابن ماجد</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-05-16 11:12:56.005</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1438178514</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>@Eng_H22</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>هدى لؤي شاكر</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>الجزيرة</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>الشركة العامة لموانئ العراق</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:46:59.502</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1938276557</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>@alikwiq</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>علي حسن عبدالله</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>المعقل-خمسه ميل</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-05-16 13:51:44.219</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>916692154</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>لا يوجد</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>نوار صادق حسن</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>مجمع الامل السكني</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>مديرية بريد واتصالات</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-05-16 16:58:05.648</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
